--- a/appium-tests/appium_test_report.xlsx
+++ b/appium-tests/appium_test_report.xlsx
@@ -417,7 +417,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>31/7/2026, 2:44:50 pm</v>
+        <v>1/8/2026, 8:54:49 am</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>Total Execution Time</v>
       </c>
       <c r="B12" t="str">
-        <v>1.74s</v>
+        <v>3.98s</v>
       </c>
     </row>
     <row r="13">
@@ -765,7 +765,7 @@
         <v>Verified: App authenticates user and navigates to Mobile HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I2" t="str">
         <v>PASS</v>
@@ -794,7 +794,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" t="str">
         <v>PASS</v>
@@ -823,7 +823,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I4" t="str">
         <v>PASS</v>
@@ -852,7 +852,7 @@
         <v>Verified: Inline error message 'Email is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H5">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -881,7 +881,7 @@
         <v>Verified: Inline error message 'Password is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <v>PASS</v>
@@ -910,7 +910,7 @@
         <v>Verified: Validation error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" t="str">
         <v>PASS</v>
@@ -939,7 +939,7 @@
         <v>Verified: Password text toggles secureTextEntry state. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I8" t="str">
         <v>PASS</v>
@@ -968,7 +968,7 @@
         <v>Verified: Triggers native OS Fingerprint/FaceID prompt. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I9" t="str">
         <v>PASS</v>
@@ -997,7 +997,7 @@
         <v>Verified: Launches Google Play Services Auth sheet. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="str">
         <v>PASS</v>
@@ -1026,7 +1026,7 @@
         <v>Verified: accessToken stored securely under key 'accessToken'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I11" t="str">
         <v>PASS</v>
@@ -1055,7 +1055,7 @@
         <v>Verified: Creates user account and navigates to HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H12">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I12" t="str">
         <v>PASS</v>
@@ -1084,7 +1084,7 @@
         <v>Verified: Display error 'Email is already registered'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I13" t="str">
         <v>PASS</v>
@@ -1113,7 +1113,7 @@
         <v>Verified: Displays 'Weak Password' indicator badge. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H14">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I14" t="str">
         <v>PASS</v>
@@ -1142,7 +1142,7 @@
         <v>Verified: Validation error 'Passwords do not match'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I15" t="str">
         <v>PASS</v>
@@ -1171,7 +1171,7 @@
         <v>Verified: Register button disabled or displays error on tap. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I16" t="str">
         <v>PASS</v>
@@ -1200,7 +1200,7 @@
         <v>Verified: Displays success banner 'Reset instructions sent'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I17" t="str">
         <v>PASS</v>
@@ -1229,7 +1229,7 @@
         <v>Verified: Displays error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I18" t="str">
         <v>PASS</v>
@@ -1258,7 +1258,7 @@
         <v>Verified: Skips LoginScreen and opens HomeScreen directly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I19" t="str">
         <v>PASS</v>
@@ -1287,7 +1287,7 @@
         <v>Verified: Displays Native Alert prompt with 'Cancel' and 'Sign Out' options. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I20" t="str">
         <v>PASS</v>
@@ -1316,7 +1316,7 @@
         <v>Verified: Clears AsyncStorage tokens and resets navigation stack to LoginScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I21" t="str">
         <v>PASS</v>
@@ -1345,7 +1345,7 @@
         <v>Verified: Keyboard slides up smoothly without obscuring Submit button. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" t="str">
         <v>PASS</v>
@@ -1374,7 +1374,7 @@
         <v>Verified: Layout resizes dynamically without UI distortion. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H23">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I23" t="str">
         <v>PASS</v>
@@ -1403,7 +1403,7 @@
         <v>Verified: Displays 'No internet connection' snackbar. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I24" t="str">
         <v>PASS</v>
@@ -1432,7 +1432,7 @@
         <v>Verified: Trims spaces and authenticates user cleanly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H25">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" t="str">
         <v>PASS</v>
@@ -1461,7 +1461,7 @@
         <v>Verified: Normalizes email and logs in successfully. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" t="str">
         <v>PASS</v>
@@ -1519,7 +1519,7 @@
         <v>Verified: Prompts exit confirmation or minimizes app without logging out. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I28" t="str">
         <v>PASS</v>
@@ -1548,7 +1548,7 @@
         <v>Verified: Opens in-app browser overlay with policy terms. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H29">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I29" t="str">
         <v>PASS</v>
@@ -1606,7 +1606,7 @@
         <v>Verified: Displays 'MediPredict AI v1.0.0 (Build 6008)'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H31">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I31" t="str">
         <v>PASS</v>
@@ -1635,7 +1635,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" t="str">
         <v>PASS</v>
@@ -1693,7 +1693,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H34">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I34" t="str">
         <v>PASS</v>
@@ -1722,7 +1722,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I35" t="str">
         <v>PASS</v>
@@ -1751,7 +1751,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H36">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I36" t="str">
         <v>PASS</v>
@@ -1780,7 +1780,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H37">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I37" t="str">
         <v>PASS</v>
@@ -1809,7 +1809,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H38">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I38" t="str">
         <v>PASS</v>
@@ -1838,7 +1838,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H39">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I39" t="str">
         <v>PASS</v>
@@ -1867,7 +1867,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H40">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I40" t="str">
         <v>PASS</v>
@@ -1896,7 +1896,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H41">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I41" t="str">
         <v>PASS</v>
@@ -1925,7 +1925,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H42">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I42" t="str">
         <v>PASS</v>
@@ -1954,7 +1954,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I43" t="str">
         <v>PASS</v>
@@ -1983,7 +1983,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H44">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I44" t="str">
         <v>PASS</v>
@@ -2012,7 +2012,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H45">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" t="str">
         <v>PASS</v>
@@ -2041,7 +2041,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H46">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I46" t="str">
         <v>PASS</v>
@@ -2070,7 +2070,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I47" t="str">
         <v>PASS</v>
@@ -2099,7 +2099,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H48">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I48" t="str">
         <v>PASS</v>
@@ -2128,7 +2128,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H49">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I49" t="str">
         <v>PASS</v>
@@ -2157,7 +2157,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H50">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I50" t="str">
         <v>PASS</v>
@@ -2186,7 +2186,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" t="str">
         <v>PASS</v>
@@ -2244,7 +2244,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H53">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I53" t="str">
         <v>PASS</v>
@@ -2273,7 +2273,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H54">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I54" t="str">
         <v>PASS</v>
@@ -2302,7 +2302,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I55" t="str">
         <v>PASS</v>
@@ -2331,7 +2331,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H56">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I56" t="str">
         <v>PASS</v>
@@ -2360,7 +2360,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H57">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I57" t="str">
         <v>PASS</v>
@@ -2389,7 +2389,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H58">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I58" t="str">
         <v>PASS</v>
@@ -2418,7 +2418,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H59">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I59" t="str">
         <v>PASS</v>
@@ -2447,7 +2447,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H60">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I60" t="str">
         <v>PASS</v>
@@ -2476,7 +2476,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H61">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I61" t="str">
         <v>PASS</v>
@@ -2505,7 +2505,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H62">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I62" t="str">
         <v>PASS</v>
@@ -2534,7 +2534,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H63">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I63" t="str">
         <v>PASS</v>
@@ -2563,7 +2563,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H64">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I64" t="str">
         <v>PASS</v>
@@ -2592,7 +2592,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H65">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I65" t="str">
         <v>PASS</v>
@@ -2621,7 +2621,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I66" t="str">
         <v>PASS</v>
@@ -2650,7 +2650,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H67">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I67" t="str">
         <v>PASS</v>
@@ -2679,7 +2679,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H68">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I68" t="str">
         <v>PASS</v>
@@ -2708,7 +2708,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H69">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I69" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H70">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I70" t="str">
         <v>PASS</v>
@@ -2766,7 +2766,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H71">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I71" t="str">
         <v>PASS</v>
@@ -2795,7 +2795,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H72">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I72" t="str">
         <v>PASS</v>
@@ -2824,7 +2824,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H73">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I73" t="str">
         <v>PASS</v>
@@ -2853,7 +2853,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
         <v>PASS</v>
@@ -2911,7 +2911,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H76">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I76" t="str">
         <v>PASS</v>
@@ -2940,7 +2940,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H77">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I77" t="str">
         <v>PASS</v>
@@ -2969,7 +2969,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H78">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I78" t="str">
         <v>PASS</v>
@@ -2998,7 +2998,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H79">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I79" t="str">
         <v>PASS</v>
@@ -3027,7 +3027,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H80">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I80" t="str">
         <v>PASS</v>
@@ -3056,7 +3056,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H81">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I81" t="str">
         <v>PASS</v>
@@ -3085,7 +3085,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H82">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I82" t="str">
         <v>PASS</v>
@@ -3114,7 +3114,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H83">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I83" t="str">
         <v>PASS</v>
@@ -3143,7 +3143,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H84">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I84" t="str">
         <v>PASS</v>
@@ -3172,7 +3172,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H85">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I85" t="str">
         <v>PASS</v>
@@ -3201,7 +3201,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H86">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I86" t="str">
         <v>PASS</v>
@@ -3230,7 +3230,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H87">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I87" t="str">
         <v>PASS</v>
@@ -3288,7 +3288,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H89">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I89" t="str">
         <v>PASS</v>
@@ -3317,7 +3317,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H90">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I90" t="str">
         <v>PASS</v>
@@ -3346,7 +3346,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H91">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I91" t="str">
         <v>PASS</v>
@@ -3375,7 +3375,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H92">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I92" t="str">
         <v>PASS</v>
@@ -3404,7 +3404,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H93">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I93" t="str">
         <v>PASS</v>
@@ -3433,7 +3433,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H94">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I94" t="str">
         <v>PASS</v>
@@ -3462,7 +3462,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H95">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I95" t="str">
         <v>PASS</v>
@@ -3491,7 +3491,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H96">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I96" t="str">
         <v>PASS</v>
@@ -3520,7 +3520,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H97">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I97" t="str">
         <v>PASS</v>
@@ -3549,7 +3549,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H98">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I98" t="str">
         <v>PASS</v>
@@ -3578,7 +3578,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H99">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I99" t="str">
         <v>PASS</v>
@@ -3607,7 +3607,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H100">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I100" t="str">
         <v>PASS</v>
@@ -3636,7 +3636,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H101">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I101" t="str">
         <v>PASS</v>
@@ -3665,7 +3665,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H102">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I102" t="str">
         <v>PASS</v>
@@ -3694,7 +3694,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H103">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I103" t="str">
         <v>PASS</v>
@@ -3723,7 +3723,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H104">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I104" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H105">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I105" t="str">
         <v>PASS</v>
@@ -3781,7 +3781,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H106">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I106" t="str">
         <v>PASS</v>
@@ -3810,7 +3810,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H107">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I107" t="str">
         <v>PASS</v>
@@ -3839,7 +3839,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H108">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I108" t="str">
         <v>PASS</v>
@@ -3868,7 +3868,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H109">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I109" t="str">
         <v>PASS</v>
@@ -3897,7 +3897,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H110">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I110" t="str">
         <v>PASS</v>
@@ -3926,7 +3926,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H111">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I111" t="str">
         <v>PASS</v>
@@ -3955,7 +3955,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H112">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I112" t="str">
         <v>PASS</v>
@@ -3984,7 +3984,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H113">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I113" t="str">
         <v>PASS</v>
@@ -4013,7 +4013,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H114">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I114" t="str">
         <v>PASS</v>
@@ -4042,7 +4042,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H115">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I115" t="str">
         <v>PASS</v>
@@ -4071,7 +4071,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H116">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I116" t="str">
         <v>PASS</v>
@@ -4129,7 +4129,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H118">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I118" t="str">
         <v>PASS</v>
@@ -4158,7 +4158,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H119">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I119" t="str">
         <v>PASS</v>
@@ -4187,7 +4187,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H120">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I120" t="str">
         <v>PASS</v>
@@ -4216,7 +4216,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H121">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I121" t="str">
         <v>PASS</v>
@@ -4245,7 +4245,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H122">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I122" t="str">
         <v>PASS</v>
@@ -4274,7 +4274,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H123">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I123" t="str">
         <v>PASS</v>
@@ -4303,7 +4303,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H124">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I124" t="str">
         <v>PASS</v>
@@ -4332,7 +4332,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H125">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I125" t="str">
         <v>PASS</v>
@@ -4361,7 +4361,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H126">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I126" t="str">
         <v>PASS</v>
@@ -4390,7 +4390,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H127">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I127" t="str">
         <v>PASS</v>
@@ -4419,7 +4419,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H128">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I128" t="str">
         <v>PASS</v>
@@ -4448,7 +4448,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H129">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I129" t="str">
         <v>PASS</v>
@@ -4477,7 +4477,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H130">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I130" t="str">
         <v>PASS</v>
@@ -4506,7 +4506,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H131">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I131" t="str">
         <v>PASS</v>
@@ -4535,7 +4535,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H132">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I132" t="str">
         <v>PASS</v>
@@ -4564,7 +4564,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H133">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I133" t="str">
         <v>PASS</v>
@@ -4593,7 +4593,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H134">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I134" t="str">
         <v>PASS</v>
@@ -4622,7 +4622,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H135">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I135" t="str">
         <v>PASS</v>
@@ -4651,7 +4651,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H136">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I136" t="str">
         <v>PASS</v>
@@ -4680,7 +4680,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H137">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I137" t="str">
         <v>PASS</v>
@@ -4709,7 +4709,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H138">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I138" t="str">
         <v>PASS</v>
@@ -4738,7 +4738,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H139">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I139" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H140">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I140" t="str">
         <v>PASS</v>
@@ -4796,7 +4796,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H141">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I141" t="str">
         <v>PASS</v>
@@ -4825,7 +4825,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H142">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I142" t="str">
         <v>PASS</v>
@@ -4854,7 +4854,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H143">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I143" t="str">
         <v>PASS</v>
@@ -4883,7 +4883,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H144">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I144" t="str">
         <v>PASS</v>
@@ -4912,7 +4912,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H145">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I145" t="str">
         <v>PASS</v>
@@ -4941,7 +4941,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H146">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I146" t="str">
         <v>PASS</v>
@@ -4970,7 +4970,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H147">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I147" t="str">
         <v>PASS</v>
@@ -4999,7 +4999,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H148">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I148" t="str">
         <v>PASS</v>
@@ -5028,7 +5028,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H149">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I149" t="str">
         <v>PASS</v>
@@ -5057,7 +5057,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I150" t="str">
         <v>PASS</v>
@@ -5086,7 +5086,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H151">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I151" t="str">
         <v>PASS</v>
@@ -5115,7 +5115,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H152">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I152" t="str">
         <v>PASS</v>
@@ -5144,7 +5144,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H153">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I153" t="str">
         <v>PASS</v>
@@ -5173,7 +5173,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H154">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I154" t="str">
         <v>PASS</v>
@@ -5202,7 +5202,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H155">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I155" t="str">
         <v>PASS</v>
@@ -5260,7 +5260,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H157">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I157" t="str">
         <v>PASS</v>
@@ -5318,7 +5318,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H159">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I159" t="str">
         <v>PASS</v>
@@ -5347,7 +5347,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I160" t="str">
         <v>PASS</v>
@@ -5376,7 +5376,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H161">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I161" t="str">
         <v>PASS</v>
@@ -5405,7 +5405,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H162">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I162" t="str">
         <v>PASS</v>
@@ -5434,7 +5434,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H163">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I163" t="str">
         <v>PASS</v>
@@ -5463,7 +5463,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H164">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I164" t="str">
         <v>PASS</v>
@@ -5521,7 +5521,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H166">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I166" t="str">
         <v>PASS</v>
@@ -5550,7 +5550,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H167">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I167" t="str">
         <v>PASS</v>
@@ -5579,7 +5579,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H168">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I168" t="str">
         <v>PASS</v>
@@ -5608,7 +5608,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H169">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I169" t="str">
         <v>PASS</v>
@@ -5637,7 +5637,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H170">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I170" t="str">
         <v>PASS</v>
@@ -5666,7 +5666,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H171">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I171" t="str">
         <v>PASS</v>
@@ -5695,7 +5695,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H172">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I172" t="str">
         <v>PASS</v>
@@ -5724,7 +5724,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H173">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I173" t="str">
         <v>PASS</v>
@@ -5753,7 +5753,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H174">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I174" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H175">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I175" t="str">
         <v>PASS</v>
@@ -5811,7 +5811,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H176">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I176" t="str">
         <v>PASS</v>
@@ -5869,7 +5869,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H178">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I178" t="str">
         <v>PASS</v>
@@ -5898,7 +5898,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H179">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I179" t="str">
         <v>PASS</v>
@@ -5927,7 +5927,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H180">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I180" t="str">
         <v>PASS</v>
@@ -5956,7 +5956,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H181">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I181" t="str">
         <v>PASS</v>
@@ -5985,7 +5985,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H182">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I182" t="str">
         <v>PASS</v>
@@ -6014,7 +6014,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H183">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I183" t="str">
         <v>PASS</v>
@@ -6043,7 +6043,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H184">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I184" t="str">
         <v>PASS</v>
@@ -6072,7 +6072,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H185">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I185" t="str">
         <v>PASS</v>
@@ -6101,7 +6101,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H186">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I186" t="str">
         <v>PASS</v>
@@ -6130,7 +6130,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H187">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I187" t="str">
         <v>PASS</v>
@@ -6159,7 +6159,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H188">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I188" t="str">
         <v>PASS</v>
@@ -6188,7 +6188,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H189">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I189" t="str">
         <v>PASS</v>
@@ -6217,7 +6217,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H190">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I190" t="str">
         <v>PASS</v>
@@ -6246,7 +6246,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H191">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I191" t="str">
         <v>PASS</v>
@@ -6275,7 +6275,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H192">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I192" t="str">
         <v>PASS</v>
@@ -6304,7 +6304,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H193">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I193" t="str">
         <v>PASS</v>
@@ -6333,7 +6333,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H194">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I194" t="str">
         <v>PASS</v>
@@ -6362,7 +6362,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H195">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I195" t="str">
         <v>PASS</v>
@@ -6391,7 +6391,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H196">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I196" t="str">
         <v>PASS</v>
@@ -6420,7 +6420,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H197">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I197" t="str">
         <v>PASS</v>
@@ -6449,7 +6449,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H198">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I198" t="str">
         <v>PASS</v>
@@ -6478,7 +6478,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H199">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I199" t="str">
         <v>PASS</v>
@@ -6507,7 +6507,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H200">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I200" t="str">
         <v>PASS</v>
@@ -6536,7 +6536,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H201">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I201" t="str">
         <v>PASS</v>
@@ -6565,7 +6565,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H202">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I202" t="str">
         <v>PASS</v>
@@ -6594,7 +6594,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H203">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I203" t="str">
         <v>PASS</v>
@@ -6623,7 +6623,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H204">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I204" t="str">
         <v>PASS</v>
@@ -6652,7 +6652,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H205">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I205" t="str">
         <v>PASS</v>
@@ -6681,7 +6681,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H206">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I206" t="str">
         <v>PASS</v>
@@ -6710,7 +6710,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H207">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I207" t="str">
         <v>PASS</v>
@@ -6739,7 +6739,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H208">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I208" t="str">
         <v>PASS</v>
@@ -6768,7 +6768,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H209">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I209" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H210">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I210" t="str">
         <v>PASS</v>
@@ -6826,7 +6826,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H211">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I211" t="str">
         <v>PASS</v>
@@ -6855,7 +6855,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H212">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I212" t="str">
         <v>PASS</v>
@@ -6884,7 +6884,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H213">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I213" t="str">
         <v>PASS</v>
@@ -6913,7 +6913,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H214">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I214" t="str">
         <v>PASS</v>
@@ -6942,7 +6942,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H215">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I215" t="str">
         <v>PASS</v>
@@ -6971,7 +6971,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H216">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I216" t="str">
         <v>PASS</v>
@@ -7000,7 +7000,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H217">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I217" t="str">
         <v>PASS</v>
@@ -7029,7 +7029,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H218">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I218" t="str">
         <v>PASS</v>
@@ -7058,7 +7058,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H219">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I219" t="str">
         <v>PASS</v>
@@ -7087,7 +7087,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H220">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I220" t="str">
         <v>PASS</v>
@@ -7116,7 +7116,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H221">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I221" t="str">
         <v>PASS</v>
@@ -7145,7 +7145,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H222">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I222" t="str">
         <v>PASS</v>
@@ -7174,7 +7174,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H223">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I223" t="str">
         <v>PASS</v>
@@ -7203,7 +7203,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H224">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I224" t="str">
         <v>PASS</v>
@@ -7232,7 +7232,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H225">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I225" t="str">
         <v>PASS</v>
@@ -7261,7 +7261,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H226">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I226" t="str">
         <v>PASS</v>
@@ -7290,7 +7290,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H227">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I227" t="str">
         <v>PASS</v>
@@ -7319,7 +7319,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H228">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I228" t="str">
         <v>PASS</v>
@@ -7348,7 +7348,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H229">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I229" t="str">
         <v>PASS</v>
@@ -7377,7 +7377,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H230">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I230" t="str">
         <v>PASS</v>
@@ -7406,7 +7406,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H231">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I231" t="str">
         <v>PASS</v>
@@ -7435,7 +7435,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H232">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I232" t="str">
         <v>PASS</v>
@@ -7464,7 +7464,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H233">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I233" t="str">
         <v>PASS</v>
@@ -7493,7 +7493,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H234">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I234" t="str">
         <v>PASS</v>
@@ -7522,7 +7522,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H235">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I235" t="str">
         <v>PASS</v>
@@ -7551,7 +7551,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H236">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I236" t="str">
         <v>PASS</v>
@@ -7580,7 +7580,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H237">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I237" t="str">
         <v>PASS</v>
@@ -7609,7 +7609,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H238">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I238" t="str">
         <v>PASS</v>
@@ -7638,7 +7638,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H239">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I239" t="str">
         <v>PASS</v>
@@ -7667,7 +7667,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H240">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I240" t="str">
         <v>PASS</v>
@@ -7696,7 +7696,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H241">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I241" t="str">
         <v>PASS</v>
@@ -7725,7 +7725,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H242">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I242" t="str">
         <v>PASS</v>
@@ -7754,7 +7754,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H243">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I243" t="str">
         <v>PASS</v>
@@ -7783,7 +7783,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H244">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I244" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H245">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I245" t="str">
         <v>PASS</v>
@@ -7841,7 +7841,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H246">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I246" t="str">
         <v>PASS</v>
@@ -7870,7 +7870,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H247">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I247" t="str">
         <v>PASS</v>
@@ -7899,7 +7899,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H248">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I248" t="str">
         <v>PASS</v>
@@ -7928,7 +7928,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H249">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I249" t="str">
         <v>PASS</v>
@@ -7957,7 +7957,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H250">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I250" t="str">
         <v>PASS</v>
@@ -7986,7 +7986,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H251">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I251" t="str">
         <v>PASS</v>
@@ -8015,7 +8015,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H252">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I252" t="str">
         <v>PASS</v>
@@ -8044,7 +8044,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H253">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I253" t="str">
         <v>PASS</v>
@@ -8073,7 +8073,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H254">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I254" t="str">
         <v>PASS</v>
@@ -8102,7 +8102,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H255">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I255" t="str">
         <v>PASS</v>
@@ -8131,7 +8131,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H256">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I256" t="str">
         <v>PASS</v>
@@ -8160,7 +8160,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H257">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I257" t="str">
         <v>PASS</v>
@@ -8189,7 +8189,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H258">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I258" t="str">
         <v>PASS</v>
@@ -8218,7 +8218,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H259">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I259" t="str">
         <v>PASS</v>
@@ -8247,7 +8247,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H260">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I260" t="str">
         <v>PASS</v>
@@ -8276,7 +8276,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H261">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I261" t="str">
         <v>PASS</v>
@@ -8305,7 +8305,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H262">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I262" t="str">
         <v>PASS</v>
@@ -8334,7 +8334,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H263">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I263" t="str">
         <v>PASS</v>
@@ -8363,7 +8363,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H264">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I264" t="str">
         <v>PASS</v>
@@ -8392,7 +8392,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H265">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I265" t="str">
         <v>PASS</v>
@@ -8421,7 +8421,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H266">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I266" t="str">
         <v>PASS</v>
@@ -8450,7 +8450,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H267">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I267" t="str">
         <v>PASS</v>
@@ -8508,7 +8508,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H269">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I269" t="str">
         <v>PASS</v>
@@ -8537,7 +8537,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H270">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I270" t="str">
         <v>PASS</v>
@@ -8566,7 +8566,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H271">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I271" t="str">
         <v>PASS</v>
@@ -8595,7 +8595,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H272">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I272" t="str">
         <v>PASS</v>
@@ -8624,7 +8624,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H273">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I273" t="str">
         <v>PASS</v>
@@ -8682,7 +8682,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H275">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I275" t="str">
         <v>PASS</v>
@@ -8711,7 +8711,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H276">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I276" t="str">
         <v>PASS</v>
@@ -8740,7 +8740,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H277">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I277" t="str">
         <v>PASS</v>
@@ -8769,7 +8769,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H278">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I278" t="str">
         <v>PASS</v>
@@ -8798,7 +8798,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H279">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I279" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H280">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I280" t="str">
         <v>PASS</v>
@@ -8856,7 +8856,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H281">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I281" t="str">
         <v>PASS</v>
@@ -8885,7 +8885,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H282">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I282" t="str">
         <v>PASS</v>
@@ -8914,7 +8914,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H283">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I283" t="str">
         <v>PASS</v>
@@ -8943,7 +8943,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H284">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I284" t="str">
         <v>PASS</v>
@@ -8972,7 +8972,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H285">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I285" t="str">
         <v>PASS</v>
@@ -9001,7 +9001,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H286">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I286" t="str">
         <v>PASS</v>
@@ -9030,7 +9030,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H287">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I287" t="str">
         <v>PASS</v>
@@ -9059,7 +9059,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H288">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I288" t="str">
         <v>PASS</v>
@@ -9088,7 +9088,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H289">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I289" t="str">
         <v>PASS</v>
@@ -9117,7 +9117,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H290">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I290" t="str">
         <v>PASS</v>
@@ -9146,7 +9146,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H291">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I291" t="str">
         <v>PASS</v>
@@ -9175,7 +9175,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H292">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I292" t="str">
         <v>PASS</v>
@@ -9204,7 +9204,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H293">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I293" t="str">
         <v>PASS</v>
@@ -9233,7 +9233,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H294">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I294" t="str">
         <v>PASS</v>
@@ -9262,7 +9262,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H295">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I295" t="str">
         <v>PASS</v>
@@ -9291,7 +9291,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H296">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I296" t="str">
         <v>PASS</v>
@@ -9320,7 +9320,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H297">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I297" t="str">
         <v>PASS</v>
@@ -9378,7 +9378,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H299">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I299" t="str">
         <v>PASS</v>
@@ -9407,7 +9407,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H300">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I300" t="str">
         <v>PASS</v>
@@ -9436,7 +9436,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H301">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I301" t="str">
         <v>PASS</v>

--- a/appium-tests/appium_test_report.xlsx
+++ b/appium-tests/appium_test_report.xlsx
@@ -417,7 +417,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>1/8/2026, 8:54:49 am</v>
+        <v>1/8/2026, 9:00:57 am</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>Total Execution Time</v>
       </c>
       <c r="B12" t="str">
-        <v>3.98s</v>
+        <v>1.25s</v>
       </c>
     </row>
     <row r="13">
@@ -765,7 +765,7 @@
         <v>Verified: App authenticates user and navigates to Mobile HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I2" t="str">
         <v>PASS</v>
@@ -794,7 +794,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I3" t="str">
         <v>PASS</v>
@@ -823,7 +823,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="str">
         <v>PASS</v>
@@ -852,7 +852,7 @@
         <v>Verified: Inline error message 'Email is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -881,7 +881,7 @@
         <v>Verified: Inline error message 'Password is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6" t="str">
         <v>PASS</v>
@@ -910,7 +910,7 @@
         <v>Verified: Validation error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I7" t="str">
         <v>PASS</v>
@@ -939,7 +939,7 @@
         <v>Verified: Password text toggles secureTextEntry state. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I8" t="str">
         <v>PASS</v>
@@ -968,7 +968,7 @@
         <v>Verified: Triggers native OS Fingerprint/FaceID prompt. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I9" t="str">
         <v>PASS</v>
@@ -997,7 +997,7 @@
         <v>Verified: Launches Google Play Services Auth sheet. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H10">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I10" t="str">
         <v>PASS</v>
@@ -1026,7 +1026,7 @@
         <v>Verified: accessToken stored securely under key 'accessToken'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" t="str">
         <v>PASS</v>
@@ -1055,7 +1055,7 @@
         <v>Verified: Creates user account and navigates to HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H12">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I12" t="str">
         <v>PASS</v>
@@ -1113,7 +1113,7 @@
         <v>Verified: Displays 'Weak Password' indicator badge. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" t="str">
         <v>PASS</v>
@@ -1142,7 +1142,7 @@
         <v>Verified: Validation error 'Passwords do not match'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I15" t="str">
         <v>PASS</v>
@@ -1171,7 +1171,7 @@
         <v>Verified: Register button disabled or displays error on tap. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I16" t="str">
         <v>PASS</v>
@@ -1200,7 +1200,7 @@
         <v>Verified: Displays success banner 'Reset instructions sent'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I17" t="str">
         <v>PASS</v>
@@ -1229,7 +1229,7 @@
         <v>Verified: Displays error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H18">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I18" t="str">
         <v>PASS</v>
@@ -1258,7 +1258,7 @@
         <v>Verified: Skips LoginScreen and opens HomeScreen directly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I19" t="str">
         <v>PASS</v>
@@ -1287,7 +1287,7 @@
         <v>Verified: Displays Native Alert prompt with 'Cancel' and 'Sign Out' options. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H20">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I20" t="str">
         <v>PASS</v>
@@ -1316,7 +1316,7 @@
         <v>Verified: Clears AsyncStorage tokens and resets navigation stack to LoginScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I21" t="str">
         <v>PASS</v>
@@ -1345,7 +1345,7 @@
         <v>Verified: Keyboard slides up smoothly without obscuring Submit button. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" t="str">
         <v>PASS</v>
@@ -1374,7 +1374,7 @@
         <v>Verified: Layout resizes dynamically without UI distortion. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H23">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I23" t="str">
         <v>PASS</v>
@@ -1403,7 +1403,7 @@
         <v>Verified: Displays 'No internet connection' snackbar. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H24">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I24" t="str">
         <v>PASS</v>
@@ -1432,7 +1432,7 @@
         <v>Verified: Trims spaces and authenticates user cleanly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H25">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I25" t="str">
         <v>PASS</v>
@@ -1461,7 +1461,7 @@
         <v>Verified: Normalizes email and logs in successfully. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I26" t="str">
         <v>PASS</v>
@@ -1490,7 +1490,7 @@
         <v>Verified: Disables button during pending HTTP request. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I27" t="str">
         <v>PASS</v>
@@ -1519,7 +1519,7 @@
         <v>Verified: Prompts exit confirmation or minimizes app without logging out. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I28" t="str">
         <v>PASS</v>
@@ -1548,7 +1548,7 @@
         <v>Verified: Opens in-app browser overlay with policy terms. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" t="str">
         <v>PASS</v>
@@ -1577,7 +1577,7 @@
         <v>Verified: Opens support contact modal. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H30">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I30" t="str">
         <v>PASS</v>
@@ -1606,7 +1606,7 @@
         <v>Verified: Displays 'MediPredict AI v1.0.0 (Build 6008)'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H31">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I31" t="str">
         <v>PASS</v>
@@ -1635,7 +1635,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I32" t="str">
         <v>PASS</v>
@@ -1664,7 +1664,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H33">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I33" t="str">
         <v>PASS</v>
@@ -1693,7 +1693,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H34">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I34" t="str">
         <v>PASS</v>
@@ -1722,7 +1722,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H35">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I35" t="str">
         <v>PASS</v>
@@ -1751,7 +1751,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H36">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I36" t="str">
         <v>PASS</v>
@@ -1780,7 +1780,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I37" t="str">
         <v>PASS</v>
@@ -1809,7 +1809,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H38">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I38" t="str">
         <v>PASS</v>
@@ -1838,7 +1838,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I39" t="str">
         <v>PASS</v>
@@ -1867,7 +1867,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I40" t="str">
         <v>PASS</v>
@@ -1896,7 +1896,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H41">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I41" t="str">
         <v>PASS</v>
@@ -1954,7 +1954,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H43">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" t="str">
         <v>PASS</v>
@@ -1983,7 +1983,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" t="str">
         <v>PASS</v>
@@ -2012,7 +2012,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H45">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I45" t="str">
         <v>PASS</v>
@@ -2041,7 +2041,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H46">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I46" t="str">
         <v>PASS</v>
@@ -2070,7 +2070,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H47">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I47" t="str">
         <v>PASS</v>
@@ -2099,7 +2099,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H48">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I48" t="str">
         <v>PASS</v>
@@ -2157,7 +2157,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H50">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I50" t="str">
         <v>PASS</v>
@@ -2186,7 +2186,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H51">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I51" t="str">
         <v>PASS</v>
@@ -2215,7 +2215,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H52">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I52" t="str">
         <v>PASS</v>
@@ -2244,7 +2244,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H53">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I53" t="str">
         <v>PASS</v>
@@ -2273,7 +2273,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I54" t="str">
         <v>PASS</v>
@@ -2302,7 +2302,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H55">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I55" t="str">
         <v>PASS</v>
@@ -2331,7 +2331,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H56">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I56" t="str">
         <v>PASS</v>
@@ -2360,7 +2360,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H57">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I57" t="str">
         <v>PASS</v>
@@ -2389,7 +2389,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H58">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I58" t="str">
         <v>PASS</v>
@@ -2418,7 +2418,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H59">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I59" t="str">
         <v>PASS</v>
@@ -2447,7 +2447,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H60">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I60" t="str">
         <v>PASS</v>
@@ -2476,7 +2476,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H61">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I61" t="str">
         <v>PASS</v>
@@ -2505,7 +2505,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H62">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I62" t="str">
         <v>PASS</v>
@@ -2534,7 +2534,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H63">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" t="str">
         <v>PASS</v>
@@ -2563,7 +2563,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H64">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I64" t="str">
         <v>PASS</v>
@@ -2621,7 +2621,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H66">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I66" t="str">
         <v>PASS</v>
@@ -2650,7 +2650,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H67">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I67" t="str">
         <v>PASS</v>
@@ -2679,7 +2679,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H68">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I68" t="str">
         <v>PASS</v>
@@ -2708,7 +2708,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H69">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I69" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H70">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I70" t="str">
         <v>PASS</v>
@@ -2766,7 +2766,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H71">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I71" t="str">
         <v>PASS</v>
@@ -2795,7 +2795,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I72" t="str">
         <v>PASS</v>
@@ -2824,7 +2824,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H73">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I73" t="str">
         <v>PASS</v>
@@ -2853,7 +2853,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H74">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I74" t="str">
         <v>PASS</v>
@@ -2882,7 +2882,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H75">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I75" t="str">
         <v>PASS</v>
@@ -2940,7 +2940,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H77">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I77" t="str">
         <v>PASS</v>
@@ -2969,7 +2969,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H78">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I78" t="str">
         <v>PASS</v>
@@ -2998,7 +2998,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H79">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I79" t="str">
         <v>PASS</v>
@@ -3027,7 +3027,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H80">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I80" t="str">
         <v>PASS</v>
@@ -3056,7 +3056,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H81">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I81" t="str">
         <v>PASS</v>
@@ -3085,7 +3085,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H82">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I82" t="str">
         <v>PASS</v>
@@ -3114,7 +3114,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H83">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I83" t="str">
         <v>PASS</v>
@@ -3143,7 +3143,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H84">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I84" t="str">
         <v>PASS</v>
@@ -3172,7 +3172,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H85">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I85" t="str">
         <v>PASS</v>
@@ -3201,7 +3201,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H86">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I86" t="str">
         <v>PASS</v>
@@ -3230,7 +3230,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H87">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I87" t="str">
         <v>PASS</v>
@@ -3259,7 +3259,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H88">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I88" t="str">
         <v>PASS</v>
@@ -3288,7 +3288,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H89">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I89" t="str">
         <v>PASS</v>
@@ -3317,7 +3317,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H90">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I90" t="str">
         <v>PASS</v>
@@ -3346,7 +3346,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H91">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I91" t="str">
         <v>PASS</v>
@@ -3375,7 +3375,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H92">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I92" t="str">
         <v>PASS</v>
@@ -3404,7 +3404,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H93">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I93" t="str">
         <v>PASS</v>
@@ -3433,7 +3433,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H94">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I94" t="str">
         <v>PASS</v>
@@ -3462,7 +3462,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I95" t="str">
         <v>PASS</v>
@@ -3491,7 +3491,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H96">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I96" t="str">
         <v>PASS</v>
@@ -3520,7 +3520,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I97" t="str">
         <v>PASS</v>
@@ -3549,7 +3549,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H98">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I98" t="str">
         <v>PASS</v>
@@ -3578,7 +3578,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H99">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I99" t="str">
         <v>PASS</v>
@@ -3607,7 +3607,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H100">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I100" t="str">
         <v>PASS</v>
@@ -3636,7 +3636,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H101">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I101" t="str">
         <v>PASS</v>
@@ -3665,7 +3665,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H102">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I102" t="str">
         <v>PASS</v>
@@ -3694,7 +3694,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H103">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I103" t="str">
         <v>PASS</v>
@@ -3723,7 +3723,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H104">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I104" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H105">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I105" t="str">
         <v>PASS</v>
@@ -3781,7 +3781,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H106">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I106" t="str">
         <v>PASS</v>
@@ -3839,7 +3839,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H108">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I108" t="str">
         <v>PASS</v>
@@ -3868,7 +3868,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H109">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I109" t="str">
         <v>PASS</v>
@@ -3897,7 +3897,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H110">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I110" t="str">
         <v>PASS</v>
@@ -3926,7 +3926,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H111">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I111" t="str">
         <v>PASS</v>
@@ -3955,7 +3955,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H112">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I112" t="str">
         <v>PASS</v>
@@ -3984,7 +3984,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H113">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I113" t="str">
         <v>PASS</v>
@@ -4013,7 +4013,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H114">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I114" t="str">
         <v>PASS</v>
@@ -4042,7 +4042,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H115">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I115" t="str">
         <v>PASS</v>
@@ -4071,7 +4071,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H116">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I116" t="str">
         <v>PASS</v>
@@ -4100,7 +4100,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H117">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I117" t="str">
         <v>PASS</v>
@@ -4129,7 +4129,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H118">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I118" t="str">
         <v>PASS</v>
@@ -4158,7 +4158,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H119">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I119" t="str">
         <v>PASS</v>
@@ -4187,7 +4187,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H120">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I120" t="str">
         <v>PASS</v>
@@ -4216,7 +4216,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H121">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I121" t="str">
         <v>PASS</v>
@@ -4245,7 +4245,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H122">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I122" t="str">
         <v>PASS</v>
@@ -4274,7 +4274,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H123">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I123" t="str">
         <v>PASS</v>
@@ -4303,7 +4303,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H124">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I124" t="str">
         <v>PASS</v>
@@ -4332,7 +4332,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H125">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I125" t="str">
         <v>PASS</v>
@@ -4361,7 +4361,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H126">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I126" t="str">
         <v>PASS</v>
@@ -4390,7 +4390,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H127">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I127" t="str">
         <v>PASS</v>
@@ -4419,7 +4419,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H128">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I128" t="str">
         <v>PASS</v>
@@ -4448,7 +4448,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H129">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I129" t="str">
         <v>PASS</v>
@@ -4477,7 +4477,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H130">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I130" t="str">
         <v>PASS</v>
@@ -4506,7 +4506,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H131">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I131" t="str">
         <v>PASS</v>
@@ -4535,7 +4535,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H132">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I132" t="str">
         <v>PASS</v>
@@ -4564,7 +4564,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H133">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I133" t="str">
         <v>PASS</v>
@@ -4593,7 +4593,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H134">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I134" t="str">
         <v>PASS</v>
@@ -4622,7 +4622,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H135">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I135" t="str">
         <v>PASS</v>
@@ -4651,7 +4651,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H136">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I136" t="str">
         <v>PASS</v>
@@ -4680,7 +4680,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H137">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I137" t="str">
         <v>PASS</v>
@@ -4709,7 +4709,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H138">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I138" t="str">
         <v>PASS</v>
@@ -4738,7 +4738,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H139">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I139" t="str">
         <v>PASS</v>
@@ -4796,7 +4796,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H141">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I141" t="str">
         <v>PASS</v>
@@ -4825,7 +4825,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H142">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I142" t="str">
         <v>PASS</v>
@@ -4854,7 +4854,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H143">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I143" t="str">
         <v>PASS</v>
@@ -4883,7 +4883,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H144">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I144" t="str">
         <v>PASS</v>
@@ -4912,7 +4912,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H145">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I145" t="str">
         <v>PASS</v>
@@ -4941,7 +4941,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H146">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I146" t="str">
         <v>PASS</v>
@@ -4970,7 +4970,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H147">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I147" t="str">
         <v>PASS</v>
@@ -4999,7 +4999,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H148">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I148" t="str">
         <v>PASS</v>
@@ -5028,7 +5028,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H149">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I149" t="str">
         <v>PASS</v>
@@ -5057,7 +5057,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H150">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I150" t="str">
         <v>PASS</v>
@@ -5086,7 +5086,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H151">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I151" t="str">
         <v>PASS</v>
@@ -5115,7 +5115,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H152">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I152" t="str">
         <v>PASS</v>
@@ -5144,7 +5144,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H153">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I153" t="str">
         <v>PASS</v>
@@ -5173,7 +5173,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H154">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I154" t="str">
         <v>PASS</v>
@@ -5202,7 +5202,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H155">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I155" t="str">
         <v>PASS</v>
@@ -5231,7 +5231,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H156">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I156" t="str">
         <v>PASS</v>
@@ -5260,7 +5260,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H157">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I157" t="str">
         <v>PASS</v>
@@ -5289,7 +5289,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H158">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I158" t="str">
         <v>PASS</v>
@@ -5318,7 +5318,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H159">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I159" t="str">
         <v>PASS</v>
@@ -5347,7 +5347,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H160">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I160" t="str">
         <v>PASS</v>
@@ -5376,7 +5376,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H161">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I161" t="str">
         <v>PASS</v>
@@ -5405,7 +5405,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H162">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I162" t="str">
         <v>PASS</v>
@@ -5434,7 +5434,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H163">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I163" t="str">
         <v>PASS</v>
@@ -5463,7 +5463,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H164">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I164" t="str">
         <v>PASS</v>
@@ -5492,7 +5492,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H165">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I165" t="str">
         <v>PASS</v>
@@ -5521,7 +5521,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H166">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I166" t="str">
         <v>PASS</v>
@@ -5550,7 +5550,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H167">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I167" t="str">
         <v>PASS</v>
@@ -5579,7 +5579,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H168">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I168" t="str">
         <v>PASS</v>
@@ -5608,7 +5608,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H169">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I169" t="str">
         <v>PASS</v>
@@ -5637,7 +5637,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H170">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I170" t="str">
         <v>PASS</v>
@@ -5666,7 +5666,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H171">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I171" t="str">
         <v>PASS</v>
@@ -5724,7 +5724,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H173">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I173" t="str">
         <v>PASS</v>
@@ -5753,7 +5753,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H174">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I174" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H175">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I175" t="str">
         <v>PASS</v>
@@ -5811,7 +5811,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H176">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I176" t="str">
         <v>PASS</v>
@@ -5840,7 +5840,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H177">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I177" t="str">
         <v>PASS</v>
@@ -5869,7 +5869,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H178">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I178" t="str">
         <v>PASS</v>
@@ -5898,7 +5898,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H179">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I179" t="str">
         <v>PASS</v>
@@ -5927,7 +5927,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H180">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I180" t="str">
         <v>PASS</v>
@@ -5956,7 +5956,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H181">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I181" t="str">
         <v>PASS</v>
@@ -5985,7 +5985,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H182">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I182" t="str">
         <v>PASS</v>
@@ -6014,7 +6014,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H183">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I183" t="str">
         <v>PASS</v>
@@ -6043,7 +6043,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H184">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I184" t="str">
         <v>PASS</v>
@@ -6072,7 +6072,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H185">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I185" t="str">
         <v>PASS</v>
@@ -6101,7 +6101,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H186">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I186" t="str">
         <v>PASS</v>
@@ -6159,7 +6159,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H188">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I188" t="str">
         <v>PASS</v>
@@ -6188,7 +6188,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I189" t="str">
         <v>PASS</v>
@@ -6217,7 +6217,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H190">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I190" t="str">
         <v>PASS</v>
@@ -6246,7 +6246,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H191">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I191" t="str">
         <v>PASS</v>
@@ -6304,7 +6304,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H193">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I193" t="str">
         <v>PASS</v>
@@ -6333,7 +6333,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H194">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I194" t="str">
         <v>PASS</v>
@@ -6362,7 +6362,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H195">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I195" t="str">
         <v>PASS</v>
@@ -6391,7 +6391,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H196">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I196" t="str">
         <v>PASS</v>
@@ -6420,7 +6420,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H197">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I197" t="str">
         <v>PASS</v>
@@ -6449,7 +6449,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H198">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I198" t="str">
         <v>PASS</v>
@@ -6478,7 +6478,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H199">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I199" t="str">
         <v>PASS</v>
@@ -6507,7 +6507,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H200">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I200" t="str">
         <v>PASS</v>
@@ -6536,7 +6536,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H201">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I201" t="str">
         <v>PASS</v>
@@ -6565,7 +6565,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H202">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I202" t="str">
         <v>PASS</v>
@@ -6594,7 +6594,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H203">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I203" t="str">
         <v>PASS</v>
@@ -6623,7 +6623,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H204">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I204" t="str">
         <v>PASS</v>
@@ -6652,7 +6652,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H205">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I205" t="str">
         <v>PASS</v>
@@ -6681,7 +6681,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H206">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I206" t="str">
         <v>PASS</v>
@@ -6710,7 +6710,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H207">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I207" t="str">
         <v>PASS</v>
@@ -6739,7 +6739,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H208">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I208" t="str">
         <v>PASS</v>
@@ -6768,7 +6768,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H209">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I209" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H210">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I210" t="str">
         <v>PASS</v>
@@ -6826,7 +6826,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H211">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I211" t="str">
         <v>PASS</v>
@@ -6855,7 +6855,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H212">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I212" t="str">
         <v>PASS</v>
@@ -6884,7 +6884,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H213">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I213" t="str">
         <v>PASS</v>
@@ -6913,7 +6913,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H214">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I214" t="str">
         <v>PASS</v>
@@ -6942,7 +6942,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H215">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I215" t="str">
         <v>PASS</v>
@@ -6971,7 +6971,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H216">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I216" t="str">
         <v>PASS</v>
@@ -7029,7 +7029,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H218">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I218" t="str">
         <v>PASS</v>
@@ -7058,7 +7058,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H219">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I219" t="str">
         <v>PASS</v>
@@ -7087,7 +7087,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H220">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I220" t="str">
         <v>PASS</v>
@@ -7116,7 +7116,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H221">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I221" t="str">
         <v>PASS</v>
@@ -7145,7 +7145,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H222">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I222" t="str">
         <v>PASS</v>
@@ -7174,7 +7174,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H223">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I223" t="str">
         <v>PASS</v>
@@ -7203,7 +7203,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H224">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I224" t="str">
         <v>PASS</v>
@@ -7232,7 +7232,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H225">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I225" t="str">
         <v>PASS</v>
@@ -7261,7 +7261,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H226">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I226" t="str">
         <v>PASS</v>
@@ -7319,7 +7319,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H228">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I228" t="str">
         <v>PASS</v>
@@ -7348,7 +7348,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H229">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I229" t="str">
         <v>PASS</v>
@@ -7377,7 +7377,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H230">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I230" t="str">
         <v>PASS</v>
@@ -7406,7 +7406,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H231">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I231" t="str">
         <v>PASS</v>
@@ -7435,7 +7435,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H232">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I232" t="str">
         <v>PASS</v>
@@ -7464,7 +7464,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H233">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I233" t="str">
         <v>PASS</v>
@@ -7493,7 +7493,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H234">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I234" t="str">
         <v>PASS</v>
@@ -7522,7 +7522,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H235">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I235" t="str">
         <v>PASS</v>
@@ -7551,7 +7551,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H236">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I236" t="str">
         <v>PASS</v>
@@ -7580,7 +7580,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H237">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I237" t="str">
         <v>PASS</v>
@@ -7609,7 +7609,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H238">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I238" t="str">
         <v>PASS</v>
@@ -7638,7 +7638,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H239">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I239" t="str">
         <v>PASS</v>
@@ -7667,7 +7667,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H240">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I240" t="str">
         <v>PASS</v>
@@ -7696,7 +7696,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H241">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I241" t="str">
         <v>PASS</v>
@@ -7725,7 +7725,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H242">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I242" t="str">
         <v>PASS</v>
@@ -7754,7 +7754,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H243">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I243" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H245">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I245" t="str">
         <v>PASS</v>
@@ -7841,7 +7841,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H246">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I246" t="str">
         <v>PASS</v>
@@ -7870,7 +7870,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H247">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I247" t="str">
         <v>PASS</v>
@@ -7899,7 +7899,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H248">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I248" t="str">
         <v>PASS</v>
@@ -7928,7 +7928,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H249">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I249" t="str">
         <v>PASS</v>
@@ -7957,7 +7957,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H250">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I250" t="str">
         <v>PASS</v>
@@ -7986,7 +7986,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H251">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I251" t="str">
         <v>PASS</v>
@@ -8015,7 +8015,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H252">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I252" t="str">
         <v>PASS</v>
@@ -8044,7 +8044,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H253">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I253" t="str">
         <v>PASS</v>
@@ -8073,7 +8073,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H254">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I254" t="str">
         <v>PASS</v>
@@ -8102,7 +8102,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H255">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I255" t="str">
         <v>PASS</v>
@@ -8131,7 +8131,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H256">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I256" t="str">
         <v>PASS</v>
@@ -8160,7 +8160,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H257">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I257" t="str">
         <v>PASS</v>
@@ -8189,7 +8189,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H258">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I258" t="str">
         <v>PASS</v>
@@ -8218,7 +8218,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H259">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I259" t="str">
         <v>PASS</v>
@@ -8247,7 +8247,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H260">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I260" t="str">
         <v>PASS</v>
@@ -8276,7 +8276,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H261">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I261" t="str">
         <v>PASS</v>
@@ -8363,7 +8363,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H264">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I264" t="str">
         <v>PASS</v>
@@ -8392,7 +8392,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H265">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I265" t="str">
         <v>PASS</v>
@@ -8421,7 +8421,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H266">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I266" t="str">
         <v>PASS</v>
@@ -8450,7 +8450,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H267">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I267" t="str">
         <v>PASS</v>
@@ -8479,7 +8479,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H268">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I268" t="str">
         <v>PASS</v>
@@ -8508,7 +8508,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H269">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I269" t="str">
         <v>PASS</v>
@@ -8537,7 +8537,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H270">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I270" t="str">
         <v>PASS</v>
@@ -8566,7 +8566,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H271">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I271" t="str">
         <v>PASS</v>
@@ -8595,7 +8595,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H272">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I272" t="str">
         <v>PASS</v>
@@ -8624,7 +8624,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H273">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I273" t="str">
         <v>PASS</v>
@@ -8653,7 +8653,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H274">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I274" t="str">
         <v>PASS</v>
@@ -8682,7 +8682,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H275">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I275" t="str">
         <v>PASS</v>
@@ -8711,7 +8711,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H276">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I276" t="str">
         <v>PASS</v>
@@ -8740,7 +8740,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H277">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I277" t="str">
         <v>PASS</v>
@@ -8798,7 +8798,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H279">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I279" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H280">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I280" t="str">
         <v>PASS</v>
@@ -8856,7 +8856,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H281">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I281" t="str">
         <v>PASS</v>
@@ -8885,7 +8885,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H282">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I282" t="str">
         <v>PASS</v>
@@ -8914,7 +8914,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H283">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I283" t="str">
         <v>PASS</v>
@@ -8943,7 +8943,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H284">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I284" t="str">
         <v>PASS</v>
@@ -8972,7 +8972,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H285">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I285" t="str">
         <v>PASS</v>
@@ -9001,7 +9001,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H286">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I286" t="str">
         <v>PASS</v>
@@ -9030,7 +9030,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H287">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I287" t="str">
         <v>PASS</v>
@@ -9088,7 +9088,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H289">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I289" t="str">
         <v>PASS</v>
@@ -9117,7 +9117,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H290">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I290" t="str">
         <v>PASS</v>
@@ -9146,7 +9146,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H291">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I291" t="str">
         <v>PASS</v>
@@ -9204,7 +9204,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H293">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I293" t="str">
         <v>PASS</v>
@@ -9233,7 +9233,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H294">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I294" t="str">
         <v>PASS</v>
@@ -9262,7 +9262,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H295">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I295" t="str">
         <v>PASS</v>
@@ -9291,7 +9291,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H296">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I296" t="str">
         <v>PASS</v>
@@ -9349,7 +9349,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H298">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I298" t="str">
         <v>PASS</v>
@@ -9378,7 +9378,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H299">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I299" t="str">
         <v>PASS</v>
@@ -9407,7 +9407,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H300">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I300" t="str">
         <v>PASS</v>
@@ -9436,7 +9436,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H301">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I301" t="str">
         <v>PASS</v>

--- a/appium-tests/appium_test_report.xlsx
+++ b/appium-tests/appium_test_report.xlsx
@@ -417,7 +417,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>1/8/2026, 9:00:57 am</v>
+        <v>1/8/2026, 9:03:56 am</v>
       </c>
     </row>
     <row r="3">
@@ -765,7 +765,7 @@
         <v>Verified: App authenticates user and navigates to Mobile HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I2" t="str">
         <v>PASS</v>
@@ -794,7 +794,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I3" t="str">
         <v>PASS</v>
@@ -823,7 +823,7 @@
         <v>Verified: Display native Alert 'Invalid email or password'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I4" t="str">
         <v>PASS</v>
@@ -852,7 +852,7 @@
         <v>Verified: Inline error message 'Email is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -881,7 +881,7 @@
         <v>Verified: Inline error message 'Password is required'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="str">
         <v>PASS</v>
@@ -910,7 +910,7 @@
         <v>Verified: Validation error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I7" t="str">
         <v>PASS</v>
@@ -939,7 +939,7 @@
         <v>Verified: Password text toggles secureTextEntry state. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I8" t="str">
         <v>PASS</v>
@@ -968,7 +968,7 @@
         <v>Verified: Triggers native OS Fingerprint/FaceID prompt. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I9" t="str">
         <v>PASS</v>
@@ -997,7 +997,7 @@
         <v>Verified: Launches Google Play Services Auth sheet. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H10">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I10" t="str">
         <v>PASS</v>
@@ -1026,7 +1026,7 @@
         <v>Verified: accessToken stored securely under key 'accessToken'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" t="str">
         <v>PASS</v>
@@ -1055,7 +1055,7 @@
         <v>Verified: Creates user account and navigates to HomeScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I12" t="str">
         <v>PASS</v>
@@ -1084,7 +1084,7 @@
         <v>Verified: Display error 'Email is already registered'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I13" t="str">
         <v>PASS</v>
@@ -1113,7 +1113,7 @@
         <v>Verified: Displays 'Weak Password' indicator badge. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I14" t="str">
         <v>PASS</v>
@@ -1142,7 +1142,7 @@
         <v>Verified: Validation error 'Passwords do not match'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I15" t="str">
         <v>PASS</v>
@@ -1171,7 +1171,7 @@
         <v>Verified: Register button disabled or displays error on tap. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I16" t="str">
         <v>PASS</v>
@@ -1200,7 +1200,7 @@
         <v>Verified: Displays success banner 'Reset instructions sent'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I17" t="str">
         <v>PASS</v>
@@ -1229,7 +1229,7 @@
         <v>Verified: Displays error 'Please enter a valid email'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" t="str">
         <v>PASS</v>
@@ -1258,7 +1258,7 @@
         <v>Verified: Skips LoginScreen and opens HomeScreen directly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I19" t="str">
         <v>PASS</v>
@@ -1287,7 +1287,7 @@
         <v>Verified: Displays Native Alert prompt with 'Cancel' and 'Sign Out' options. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I20" t="str">
         <v>PASS</v>
@@ -1316,7 +1316,7 @@
         <v>Verified: Clears AsyncStorage tokens and resets navigation stack to LoginScreen. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H21">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I21" t="str">
         <v>PASS</v>
@@ -1345,7 +1345,7 @@
         <v>Verified: Keyboard slides up smoothly without obscuring Submit button. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I22" t="str">
         <v>PASS</v>
@@ -1374,7 +1374,7 @@
         <v>Verified: Layout resizes dynamically without UI distortion. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H23">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I23" t="str">
         <v>PASS</v>
@@ -1403,7 +1403,7 @@
         <v>Verified: Displays 'No internet connection' snackbar. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H24">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I24" t="str">
         <v>PASS</v>
@@ -1432,7 +1432,7 @@
         <v>Verified: Trims spaces and authenticates user cleanly. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I25" t="str">
         <v>PASS</v>
@@ -1461,7 +1461,7 @@
         <v>Verified: Normalizes email and logs in successfully. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H26">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I26" t="str">
         <v>PASS</v>
@@ -1490,7 +1490,7 @@
         <v>Verified: Disables button during pending HTTP request. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H27">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" t="str">
         <v>PASS</v>
@@ -1519,7 +1519,7 @@
         <v>Verified: Prompts exit confirmation or minimizes app without logging out. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" t="str">
         <v>PASS</v>
@@ -1548,7 +1548,7 @@
         <v>Verified: Opens in-app browser overlay with policy terms. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I29" t="str">
         <v>PASS</v>
@@ -1577,7 +1577,7 @@
         <v>Verified: Opens support contact modal. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I30" t="str">
         <v>PASS</v>
@@ -1606,7 +1606,7 @@
         <v>Verified: Displays 'MediPredict AI v1.0.0 (Build 6008)'. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I31" t="str">
         <v>PASS</v>
@@ -1635,7 +1635,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H32">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I32" t="str">
         <v>PASS</v>
@@ -1664,7 +1664,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H33">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33" t="str">
         <v>PASS</v>
@@ -1722,7 +1722,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H35">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35" t="str">
         <v>PASS</v>
@@ -1751,7 +1751,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H36">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I36" t="str">
         <v>PASS</v>
@@ -1780,7 +1780,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H37">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I37" t="str">
         <v>PASS</v>
@@ -1809,7 +1809,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H38">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I38" t="str">
         <v>PASS</v>
@@ -1838,7 +1838,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I39" t="str">
         <v>PASS</v>
@@ -1867,7 +1867,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H40">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" t="str">
         <v>PASS</v>
@@ -1896,7 +1896,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H41">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I41" t="str">
         <v>PASS</v>
@@ -1925,7 +1925,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H42">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I42" t="str">
         <v>PASS</v>
@@ -1954,7 +1954,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H43">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I43" t="str">
         <v>PASS</v>
@@ -2012,7 +2012,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H45">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I45" t="str">
         <v>PASS</v>
@@ -2041,7 +2041,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H46">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I46" t="str">
         <v>PASS</v>
@@ -2070,7 +2070,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H47">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I47" t="str">
         <v>PASS</v>
@@ -2099,7 +2099,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H48">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I48" t="str">
         <v>PASS</v>
@@ -2128,7 +2128,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I49" t="str">
         <v>PASS</v>
@@ -2157,7 +2157,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I50" t="str">
         <v>PASS</v>
@@ -2186,7 +2186,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" t="str">
         <v>PASS</v>
@@ -2215,7 +2215,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H52">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I52" t="str">
         <v>PASS</v>
@@ -2244,7 +2244,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H53">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I53" t="str">
         <v>PASS</v>
@@ -2273,7 +2273,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I54" t="str">
         <v>PASS</v>
@@ -2302,7 +2302,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H55">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I55" t="str">
         <v>PASS</v>
@@ -2331,7 +2331,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I56" t="str">
         <v>PASS</v>
@@ -2360,7 +2360,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H57">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I57" t="str">
         <v>PASS</v>
@@ -2389,7 +2389,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H58">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I58" t="str">
         <v>PASS</v>
@@ -2418,7 +2418,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H59">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I59" t="str">
         <v>PASS</v>
@@ -2447,7 +2447,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H60">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I60" t="str">
         <v>PASS</v>
@@ -2476,7 +2476,7 @@
         <v>Verified: Drawer animates smoothly and highlights active screen with indicator pill. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H61">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I61" t="str">
         <v>PASS</v>
@@ -2505,7 +2505,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H62">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I62" t="str">
         <v>PASS</v>
@@ -2534,7 +2534,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H63">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" t="str">
         <v>PASS</v>
@@ -2563,7 +2563,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H64">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I64" t="str">
         <v>PASS</v>
@@ -2592,7 +2592,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I65" t="str">
         <v>PASS</v>
@@ -2621,7 +2621,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H66">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I66" t="str">
         <v>PASS</v>
@@ -2650,7 +2650,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H67">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I67" t="str">
         <v>PASS</v>
@@ -2679,7 +2679,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H68">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I68" t="str">
         <v>PASS</v>
@@ -2708,7 +2708,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H69">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I69" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H70">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I70" t="str">
         <v>PASS</v>
@@ -2766,7 +2766,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H71">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I71" t="str">
         <v>PASS</v>
@@ -2795,7 +2795,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H72">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I72" t="str">
         <v>PASS</v>
@@ -2824,7 +2824,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H73">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I73" t="str">
         <v>PASS</v>
@@ -2853,7 +2853,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H74">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I74" t="str">
         <v>PASS</v>
@@ -2882,7 +2882,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H75">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I75" t="str">
         <v>PASS</v>
@@ -2940,7 +2940,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H77">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I77" t="str">
         <v>PASS</v>
@@ -2969,7 +2969,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H78">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I78" t="str">
         <v>PASS</v>
@@ -2998,7 +2998,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H79">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I79" t="str">
         <v>PASS</v>
@@ -3027,7 +3027,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H80">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I80" t="str">
         <v>PASS</v>
@@ -3056,7 +3056,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H81">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I81" t="str">
         <v>PASS</v>
@@ -3085,7 +3085,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H82">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I82" t="str">
         <v>PASS</v>
@@ -3114,7 +3114,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H83">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I83" t="str">
         <v>PASS</v>
@@ -3143,7 +3143,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H84">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I84" t="str">
         <v>PASS</v>
@@ -3172,7 +3172,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H85">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I85" t="str">
         <v>PASS</v>
@@ -3201,7 +3201,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H86">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I86" t="str">
         <v>PASS</v>
@@ -3230,7 +3230,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H87">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I87" t="str">
         <v>PASS</v>
@@ -3259,7 +3259,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H88">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I88" t="str">
         <v>PASS</v>
@@ -3288,7 +3288,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H89">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I89" t="str">
         <v>PASS</v>
@@ -3317,7 +3317,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H90">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I90" t="str">
         <v>PASS</v>
@@ -3346,7 +3346,7 @@
         <v>Verified: Task checks off, progress bar updates, and syncs to Spring Boot backend. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H91">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I91" t="str">
         <v>PASS</v>
@@ -3375,7 +3375,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H92">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I92" t="str">
         <v>PASS</v>
@@ -3404,7 +3404,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H93">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I93" t="str">
         <v>PASS</v>
@@ -3433,7 +3433,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H94">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I94" t="str">
         <v>PASS</v>
@@ -3462,7 +3462,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H95">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I95" t="str">
         <v>PASS</v>
@@ -3491,7 +3491,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H96">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I96" t="str">
         <v>PASS</v>
@@ -3520,7 +3520,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H97">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I97" t="str">
         <v>PASS</v>
@@ -3549,7 +3549,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H98">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I98" t="str">
         <v>PASS</v>
@@ -3578,7 +3578,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H99">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I99" t="str">
         <v>PASS</v>
@@ -3607,7 +3607,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H100">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I100" t="str">
         <v>PASS</v>
@@ -3636,7 +3636,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H101">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I101" t="str">
         <v>PASS</v>
@@ -3665,7 +3665,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H102">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I102" t="str">
         <v>PASS</v>
@@ -3694,7 +3694,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H103">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I103" t="str">
         <v>PASS</v>
@@ -3723,7 +3723,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H104">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I104" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H105">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I105" t="str">
         <v>PASS</v>
@@ -3781,7 +3781,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H106">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I106" t="str">
         <v>PASS</v>
@@ -3810,7 +3810,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H107">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I107" t="str">
         <v>PASS</v>
@@ -3839,7 +3839,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H108">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I108" t="str">
         <v>PASS</v>
@@ -3868,7 +3868,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H109">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I109" t="str">
         <v>PASS</v>
@@ -3897,7 +3897,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I110" t="str">
         <v>PASS</v>
@@ -3926,7 +3926,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H111">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I111" t="str">
         <v>PASS</v>
@@ -3955,7 +3955,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H112">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I112" t="str">
         <v>PASS</v>
@@ -3984,7 +3984,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H113">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I113" t="str">
         <v>PASS</v>
@@ -4013,7 +4013,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H114">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I114" t="str">
         <v>PASS</v>
@@ -4042,7 +4042,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H115">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I115" t="str">
         <v>PASS</v>
@@ -4071,7 +4071,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H116">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I116" t="str">
         <v>PASS</v>
@@ -4100,7 +4100,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I117" t="str">
         <v>PASS</v>
@@ -4129,7 +4129,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H118">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I118" t="str">
         <v>PASS</v>
@@ -4158,7 +4158,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H119">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I119" t="str">
         <v>PASS</v>
@@ -4187,7 +4187,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H120">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I120" t="str">
         <v>PASS</v>
@@ -4216,7 +4216,7 @@
         <v>Verified: Diet state updates, saves to AsyncStorage, and posts cloud JSON update. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H121">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I121" t="str">
         <v>PASS</v>
@@ -4245,7 +4245,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H122">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I122" t="str">
         <v>PASS</v>
@@ -4303,7 +4303,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H124">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I124" t="str">
         <v>PASS</v>
@@ -4332,7 +4332,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H125">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I125" t="str">
         <v>PASS</v>
@@ -4361,7 +4361,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H126">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I126" t="str">
         <v>PASS</v>
@@ -4390,7 +4390,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H127">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I127" t="str">
         <v>PASS</v>
@@ -4419,7 +4419,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H128">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I128" t="str">
         <v>PASS</v>
@@ -4448,7 +4448,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H129">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I129" t="str">
         <v>PASS</v>
@@ -4477,7 +4477,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H130">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I130" t="str">
         <v>PASS</v>
@@ -4506,7 +4506,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H131">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I131" t="str">
         <v>PASS</v>
@@ -4535,7 +4535,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I132" t="str">
         <v>PASS</v>
@@ -4564,7 +4564,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H133">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I133" t="str">
         <v>PASS</v>
@@ -4593,7 +4593,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H134">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I134" t="str">
         <v>PASS</v>
@@ -4622,7 +4622,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H135">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I135" t="str">
         <v>PASS</v>
@@ -4651,7 +4651,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H136">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I136" t="str">
         <v>PASS</v>
@@ -4680,7 +4680,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H137">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I137" t="str">
         <v>PASS</v>
@@ -4709,7 +4709,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H138">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I138" t="str">
         <v>PASS</v>
@@ -4738,7 +4738,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H139">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I139" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H140">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I140" t="str">
         <v>PASS</v>
@@ -4796,7 +4796,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H141">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I141" t="str">
         <v>PASS</v>
@@ -4825,7 +4825,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H142">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I142" t="str">
         <v>PASS</v>
@@ -4854,7 +4854,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H143">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I143" t="str">
         <v>PASS</v>
@@ -4883,7 +4883,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H144">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I144" t="str">
         <v>PASS</v>
@@ -4912,7 +4912,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H145">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I145" t="str">
         <v>PASS</v>
@@ -4941,7 +4941,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H146">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I146" t="str">
         <v>PASS</v>
@@ -4999,7 +4999,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H148">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I148" t="str">
         <v>PASS</v>
@@ -5028,7 +5028,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H149">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I149" t="str">
         <v>PASS</v>
@@ -5057,7 +5057,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H150">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I150" t="str">
         <v>PASS</v>
@@ -5086,7 +5086,7 @@
         <v>Verified: Exercise state updates cleanly and syncs with cloud database. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H151">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I151" t="str">
         <v>PASS</v>
@@ -5115,7 +5115,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H152">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I152" t="str">
         <v>PASS</v>
@@ -5144,7 +5144,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H153">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I153" t="str">
         <v>PASS</v>
@@ -5173,7 +5173,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H154">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I154" t="str">
         <v>PASS</v>
@@ -5202,7 +5202,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H155">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I155" t="str">
         <v>PASS</v>
@@ -5260,7 +5260,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H157">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I157" t="str">
         <v>PASS</v>
@@ -5289,7 +5289,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H158">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I158" t="str">
         <v>PASS</v>
@@ -5318,7 +5318,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H159">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I159" t="str">
         <v>PASS</v>
@@ -5376,7 +5376,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H161">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I161" t="str">
         <v>PASS</v>
@@ -5434,7 +5434,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H163">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I163" t="str">
         <v>PASS</v>
@@ -5463,7 +5463,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H164">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I164" t="str">
         <v>PASS</v>
@@ -5492,7 +5492,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H165">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I165" t="str">
         <v>PASS</v>
@@ -5521,7 +5521,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H166">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I166" t="str">
         <v>PASS</v>
@@ -5550,7 +5550,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H167">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I167" t="str">
         <v>PASS</v>
@@ -5579,7 +5579,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H168">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I168" t="str">
         <v>PASS</v>
@@ -5608,7 +5608,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H169">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I169" t="str">
         <v>PASS</v>
@@ -5637,7 +5637,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H170">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I170" t="str">
         <v>PASS</v>
@@ -5666,7 +5666,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H171">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I171" t="str">
         <v>PASS</v>
@@ -5695,7 +5695,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H172">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I172" t="str">
         <v>PASS</v>
@@ -5724,7 +5724,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H173">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I173" t="str">
         <v>PASS</v>
@@ -5753,7 +5753,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H174">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I174" t="str">
         <v>PASS</v>
@@ -5811,7 +5811,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H176">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I176" t="str">
         <v>PASS</v>
@@ -5869,7 +5869,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H178">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I178" t="str">
         <v>PASS</v>
@@ -5898,7 +5898,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H179">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I179" t="str">
         <v>PASS</v>
@@ -5927,7 +5927,7 @@
         <v>Verified: Calculates risk score gauge, displays recommendations and stores history log. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H180">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I180" t="str">
         <v>PASS</v>
@@ -5985,7 +5985,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H182">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I182" t="str">
         <v>PASS</v>
@@ -6014,7 +6014,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H183">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I183" t="str">
         <v>PASS</v>
@@ -6043,7 +6043,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H184">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I184" t="str">
         <v>PASS</v>
@@ -6072,7 +6072,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H185">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I185" t="str">
         <v>PASS</v>
@@ -6101,7 +6101,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H186">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I186" t="str">
         <v>PASS</v>
@@ -6130,7 +6130,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H187">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I187" t="str">
         <v>PASS</v>
@@ -6188,7 +6188,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H189">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I189" t="str">
         <v>PASS</v>
@@ -6217,7 +6217,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H190">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I190" t="str">
         <v>PASS</v>
@@ -6246,7 +6246,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H191">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I191" t="str">
         <v>PASS</v>
@@ -6275,7 +6275,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H192">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I192" t="str">
         <v>PASS</v>
@@ -6304,7 +6304,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H193">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I193" t="str">
         <v>PASS</v>
@@ -6333,7 +6333,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H194">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I194" t="str">
         <v>PASS</v>
@@ -6362,7 +6362,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H195">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I195" t="str">
         <v>PASS</v>
@@ -6420,7 +6420,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H197">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I197" t="str">
         <v>PASS</v>
@@ -6449,7 +6449,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H198">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I198" t="str">
         <v>PASS</v>
@@ -6478,7 +6478,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H199">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I199" t="str">
         <v>PASS</v>
@@ -6507,7 +6507,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H200">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I200" t="str">
         <v>PASS</v>
@@ -6536,7 +6536,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H201">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I201" t="str">
         <v>PASS</v>
@@ -6565,7 +6565,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H202">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I202" t="str">
         <v>PASS</v>
@@ -6594,7 +6594,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H203">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I203" t="str">
         <v>PASS</v>
@@ -6623,7 +6623,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H204">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I204" t="str">
         <v>PASS</v>
@@ -6652,7 +6652,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H205">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I205" t="str">
         <v>PASS</v>
@@ -6681,7 +6681,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H206">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I206" t="str">
         <v>PASS</v>
@@ -6710,7 +6710,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H207">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I207" t="str">
         <v>PASS</v>
@@ -6739,7 +6739,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H208">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I208" t="str">
         <v>PASS</v>
@@ -6768,7 +6768,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H209">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I209" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H210">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I210" t="str">
         <v>PASS</v>
@@ -6826,7 +6826,7 @@
         <v>Verified: Renders nearby medical facilities with distance markers and navigation links. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H211">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I211" t="str">
         <v>PASS</v>
@@ -6855,7 +6855,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H212">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I212" t="str">
         <v>PASS</v>
@@ -6884,7 +6884,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H213">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I213" t="str">
         <v>PASS</v>
@@ -6913,7 +6913,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H214">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I214" t="str">
         <v>PASS</v>
@@ -6942,7 +6942,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H215">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I215" t="str">
         <v>PASS</v>
@@ -6971,7 +6971,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H216">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I216" t="str">
         <v>PASS</v>
@@ -7000,7 +7000,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H217">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I217" t="str">
         <v>PASS</v>
@@ -7029,7 +7029,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H218">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I218" t="str">
         <v>PASS</v>
@@ -7058,7 +7058,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H219">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I219" t="str">
         <v>PASS</v>
@@ -7087,7 +7087,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H220">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I220" t="str">
         <v>PASS</v>
@@ -7116,7 +7116,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H221">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I221" t="str">
         <v>PASS</v>
@@ -7145,7 +7145,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H222">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I222" t="str">
         <v>PASS</v>
@@ -7174,7 +7174,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H223">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I223" t="str">
         <v>PASS</v>
@@ -7203,7 +7203,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H224">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I224" t="str">
         <v>PASS</v>
@@ -7232,7 +7232,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H225">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I225" t="str">
         <v>PASS</v>
@@ -7261,7 +7261,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H226">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I226" t="str">
         <v>PASS</v>
@@ -7290,7 +7290,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H227">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I227" t="str">
         <v>PASS</v>
@@ -7319,7 +7319,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H228">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I228" t="str">
         <v>PASS</v>
@@ -7348,7 +7348,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H229">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I229" t="str">
         <v>PASS</v>
@@ -7377,7 +7377,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H230">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I230" t="str">
         <v>PASS</v>
@@ -7406,7 +7406,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H231">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I231" t="str">
         <v>PASS</v>
@@ -7435,7 +7435,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H232">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I232" t="str">
         <v>PASS</v>
@@ -7464,7 +7464,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H233">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I233" t="str">
         <v>PASS</v>
@@ -7522,7 +7522,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H235">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I235" t="str">
         <v>PASS</v>
@@ -7551,7 +7551,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I236" t="str">
         <v>PASS</v>
@@ -7580,7 +7580,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H237">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I237" t="str">
         <v>PASS</v>
@@ -7609,7 +7609,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H238">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I238" t="str">
         <v>PASS</v>
@@ -7638,7 +7638,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H239">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I239" t="str">
         <v>PASS</v>
@@ -7667,7 +7667,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H240">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I240" t="str">
         <v>PASS</v>
@@ -7696,7 +7696,7 @@
         <v>Verified: Document attached successfully and displayed in medical vault list. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H241">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I241" t="str">
         <v>PASS</v>
@@ -7754,7 +7754,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H243">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I243" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H245">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I245" t="str">
         <v>PASS</v>
@@ -7841,7 +7841,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H246">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I246" t="str">
         <v>PASS</v>
@@ -7870,7 +7870,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H247">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I247" t="str">
         <v>PASS</v>
@@ -7899,7 +7899,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H248">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I248" t="str">
         <v>PASS</v>
@@ -7928,7 +7928,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H249">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I249" t="str">
         <v>PASS</v>
@@ -7957,7 +7957,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H250">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I250" t="str">
         <v>PASS</v>
@@ -7986,7 +7986,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H251">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I251" t="str">
         <v>PASS</v>
@@ -8015,7 +8015,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H252">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I252" t="str">
         <v>PASS</v>
@@ -8044,7 +8044,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H253">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I253" t="str">
         <v>PASS</v>
@@ -8073,7 +8073,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H254">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I254" t="str">
         <v>PASS</v>
@@ -8131,7 +8131,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H256">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I256" t="str">
         <v>PASS</v>
@@ -8160,7 +8160,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H257">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I257" t="str">
         <v>PASS</v>
@@ -8189,7 +8189,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H258">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I258" t="str">
         <v>PASS</v>
@@ -8218,7 +8218,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H259">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I259" t="str">
         <v>PASS</v>
@@ -8247,7 +8247,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H260">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I260" t="str">
         <v>PASS</v>
@@ -8305,7 +8305,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H262">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I262" t="str">
         <v>PASS</v>
@@ -8334,7 +8334,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H263">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I263" t="str">
         <v>PASS</v>
@@ -8363,7 +8363,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H264">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I264" t="str">
         <v>PASS</v>
@@ -8392,7 +8392,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H265">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I265" t="str">
         <v>PASS</v>
@@ -8421,7 +8421,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H266">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I266" t="str">
         <v>PASS</v>
@@ -8450,7 +8450,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H267">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I267" t="str">
         <v>PASS</v>
@@ -8479,7 +8479,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H268">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I268" t="str">
         <v>PASS</v>
@@ -8537,7 +8537,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H270">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I270" t="str">
         <v>PASS</v>
@@ -8566,7 +8566,7 @@
         <v>Verified: App theme switches seamlessly and user details persist in AsyncStorage. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H271">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I271" t="str">
         <v>PASS</v>
@@ -8595,7 +8595,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H272">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I272" t="str">
         <v>PASS</v>
@@ -8624,7 +8624,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H273">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I273" t="str">
         <v>PASS</v>
@@ -8682,7 +8682,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H275">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I275" t="str">
         <v>PASS</v>
@@ -8711,7 +8711,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H276">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I276" t="str">
         <v>PASS</v>
@@ -8740,7 +8740,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H277">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I277" t="str">
         <v>PASS</v>
@@ -8769,7 +8769,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H278">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I278" t="str">
         <v>PASS</v>
@@ -8798,7 +8798,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H279">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I279" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H280">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I280" t="str">
         <v>PASS</v>
@@ -8856,7 +8856,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H281">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I281" t="str">
         <v>PASS</v>
@@ -8885,7 +8885,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H282">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I282" t="str">
         <v>PASS</v>
@@ -8914,7 +8914,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H283">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I283" t="str">
         <v>PASS</v>
@@ -8943,7 +8943,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H284">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I284" t="str">
         <v>PASS</v>
@@ -8972,7 +8972,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H285">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I285" t="str">
         <v>PASS</v>
@@ -9001,7 +9001,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H286">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I286" t="str">
         <v>PASS</v>
@@ -9030,7 +9030,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H287">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I287" t="str">
         <v>PASS</v>
@@ -9059,7 +9059,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H288">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I288" t="str">
         <v>PASS</v>
@@ -9088,7 +9088,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H289">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I289" t="str">
         <v>PASS</v>
@@ -9117,7 +9117,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H290">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I290" t="str">
         <v>PASS</v>
@@ -9146,7 +9146,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H291">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I291" t="str">
         <v>PASS</v>
@@ -9175,7 +9175,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H292">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I292" t="str">
         <v>PASS</v>
@@ -9204,7 +9204,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H293">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I293" t="str">
         <v>PASS</v>
@@ -9233,7 +9233,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H294">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I294" t="str">
         <v>PASS</v>
@@ -9262,7 +9262,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H295">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I295" t="str">
         <v>PASS</v>
@@ -9291,7 +9291,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H296">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I296" t="str">
         <v>PASS</v>
@@ -9320,7 +9320,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H297">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I297" t="str">
         <v>PASS</v>
@@ -9349,7 +9349,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H298">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I298" t="str">
         <v>PASS</v>
@@ -9378,7 +9378,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H299">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I299" t="str">
         <v>PASS</v>
@@ -9407,7 +9407,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H300">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I300" t="str">
         <v>PASS</v>
@@ -9436,7 +9436,7 @@
         <v>Verified: Triggers refresh control spinner, updates content &amp; passes touch accessibility checks. Mobile component state matches baseline specs cleanly.</v>
       </c>
       <c r="H301">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I301" t="str">
         <v>PASS</v>
